--- a/data/availability/projects/m-squared-developments/31-west.xlsx
+++ b/data/availability/projects/m-squared-developments/31-west.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Twinhouse</t>
+          <t>Twin House</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -959,7 +959,6 @@
       <c r="G2" t="n">
         <v>140</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -970,7 +969,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1016,7 +1015,6 @@
       <c r="G3" t="n">
         <v>140</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1027,7 +1025,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1073,7 +1071,6 @@
       <c r="G4" t="n">
         <v>135</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1084,7 +1081,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1130,7 +1127,6 @@
       <c r="G5" t="n">
         <v>135</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1141,7 +1137,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1187,7 +1183,6 @@
       <c r="G6" t="n">
         <v>130</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1198,7 +1193,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1244,7 +1239,6 @@
       <c r="G7" t="n">
         <v>130</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1255,7 +1249,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1301,7 +1295,6 @@
       <c r="G8" t="n">
         <v>140</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1312,7 +1305,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1358,7 +1351,6 @@
       <c r="G9" t="n">
         <v>140</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1369,7 +1361,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1415,7 +1407,6 @@
       <c r="G10" t="n">
         <v>135</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1426,7 +1417,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1472,7 +1463,6 @@
       <c r="G11" t="n">
         <v>135</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1483,7 +1473,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1529,7 +1519,6 @@
       <c r="G12" t="n">
         <v>130</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1540,7 +1529,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1586,7 +1575,6 @@
       <c r="G13" t="n">
         <v>130</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1597,7 +1585,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1643,7 +1631,6 @@
       <c r="G14" t="n">
         <v>165</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1654,7 +1641,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1700,7 +1687,6 @@
       <c r="G15" t="n">
         <v>136</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1711,7 +1697,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1757,7 +1743,6 @@
       <c r="G16" t="n">
         <v>165</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1768,7 +1753,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1814,7 +1799,6 @@
       <c r="G17" t="n">
         <v>129</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1825,7 +1809,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1871,7 +1855,6 @@
       <c r="G18" t="n">
         <v>129</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1882,7 +1865,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1928,7 +1911,6 @@
       <c r="G19" t="n">
         <v>90</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1939,7 +1921,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1985,7 +1967,6 @@
       <c r="G20" t="n">
         <v>140</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1996,7 +1977,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2042,7 +2023,6 @@
       <c r="G21" t="n">
         <v>140</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2053,7 +2033,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2099,7 +2079,6 @@
       <c r="G22" t="n">
         <v>135</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2110,7 +2089,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2156,7 +2135,6 @@
       <c r="G23" t="n">
         <v>135</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2167,7 +2145,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2213,7 +2191,6 @@
       <c r="G24" t="n">
         <v>130</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2224,7 +2201,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2270,7 +2247,6 @@
       <c r="G25" t="n">
         <v>165</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2281,7 +2257,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2327,7 +2303,6 @@
       <c r="G26" t="n">
         <v>160</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2338,7 +2313,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2384,7 +2359,6 @@
       <c r="G27" t="n">
         <v>155</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2395,7 +2369,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2417,7 +2391,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2441,7 +2415,6 @@
       <c r="G28" t="n">
         <v>330</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2452,7 +2425,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2474,7 +2447,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Twinhouse</t>
+          <t>Twin House</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2498,7 +2471,6 @@
       <c r="G29" t="n">
         <v>275</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2509,7 +2481,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2555,7 +2527,6 @@
       <c r="G30" t="n">
         <v>225</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2566,7 +2537,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2612,7 +2583,6 @@
       <c r="G31" t="n">
         <v>225</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2623,7 +2593,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2669,7 +2639,6 @@
       <c r="G32" t="n">
         <v>225</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2680,7 +2649,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2726,7 +2695,6 @@
       <c r="G33" t="n">
         <v>225</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2737,7 +2705,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2783,7 +2751,6 @@
       <c r="G34" t="n">
         <v>225</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2794,7 +2761,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2840,7 +2807,6 @@
       <c r="G35" t="n">
         <v>115</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2851,7 +2817,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2897,7 +2863,6 @@
       <c r="G36" t="n">
         <v>125</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2908,7 +2873,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2954,7 +2919,6 @@
       <c r="G37" t="n">
         <v>120</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2965,7 +2929,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3011,7 +2975,6 @@
       <c r="G38" t="n">
         <v>115</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3022,7 +2985,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3068,7 +3031,6 @@
       <c r="G39" t="n">
         <v>125</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3079,7 +3041,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3125,7 +3087,6 @@
       <c r="G40" t="n">
         <v>120</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3136,7 +3097,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3182,7 +3143,6 @@
       <c r="G41" t="n">
         <v>80</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3193,7 +3153,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3239,7 +3199,6 @@
       <c r="G42" t="n">
         <v>90</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3250,7 +3209,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3296,7 +3255,6 @@
       <c r="G43" t="n">
         <v>140</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3307,7 +3265,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3353,7 +3311,6 @@
       <c r="G44" t="n">
         <v>180</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3364,7 +3321,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3410,7 +3367,6 @@
       <c r="G45" t="n">
         <v>150</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3421,7 +3377,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3467,7 +3423,6 @@
       <c r="G46" t="n">
         <v>150</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3478,7 +3433,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3524,7 +3479,6 @@
       <c r="G47" t="n">
         <v>140</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3535,7 +3489,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3581,7 +3535,6 @@
       <c r="G48" t="n">
         <v>145</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3592,7 +3545,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3638,7 +3591,6 @@
       <c r="G49" t="n">
         <v>145</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3649,7 +3601,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3695,7 +3647,6 @@
       <c r="G50" t="n">
         <v>135</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3706,7 +3657,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3752,7 +3703,6 @@
       <c r="G51" t="n">
         <v>140</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3763,7 +3713,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3809,7 +3759,6 @@
       <c r="G52" t="n">
         <v>140</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3820,7 +3769,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3866,7 +3815,6 @@
       <c r="G53" t="n">
         <v>165</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3877,7 +3825,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3923,7 +3871,6 @@
       <c r="G54" t="n">
         <v>136</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3934,7 +3881,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3980,7 +3927,6 @@
       <c r="G55" t="n">
         <v>165</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3991,7 +3937,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4037,7 +3983,6 @@
       <c r="G56" t="n">
         <v>165</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4048,7 +3993,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4094,7 +4039,6 @@
       <c r="G57" t="n">
         <v>129</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4105,7 +4049,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4151,7 +4095,6 @@
       <c r="G58" t="n">
         <v>160</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4162,7 +4105,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4208,7 +4151,6 @@
       <c r="G59" t="n">
         <v>160</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4219,7 +4161,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4265,7 +4207,6 @@
       <c r="G60" t="n">
         <v>129</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4276,7 +4217,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4322,7 +4263,6 @@
       <c r="G61" t="n">
         <v>155</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4333,7 +4273,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4379,7 +4319,6 @@
       <c r="G62" t="n">
         <v>155</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4390,7 +4329,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
